--- a/tests/workbooktests/workbooks/test_daycounters.xlsx
+++ b/tests/workbooktests/workbooks/test_daycounters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D7B15E-D2DC-42E3-9EDE-3170C9A9B297}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07320061-45E5-4D65-A3DD-85A49E2B67B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10905" xr2:uid="{59CE0412-DF39-40A8-8B92-B52EBF7D2CB4}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{59CE0412-DF39-40A8-8B92-B52EBF7D2CB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,20 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -129,7 +143,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -145,9 +159,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -185,7 +199,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -291,7 +305,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -433,7 +447,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -442,19 +456,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{564A54B1-D648-422B-ABA0-8175C08665E2}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" customWidth="1"/>
     <col min="6" max="6" width="39" customWidth="1"/>
     <col min="7" max="7" width="43" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" customWidth="1"/>
+    <col min="8" max="8" width="21.109375" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="32.7109375" customWidth="1"/>
+    <col min="10" max="10" width="32.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -463,7 +477,7 @@
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -472,10 +486,10 @@
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>19</v>
       </c>
@@ -501,367 +515,367 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>0</v>
       </c>
-      <c r="D5" t="str">
-        <f>_xll.qlDayCounter(C5)</f>
-        <v>Actual/360</v>
-      </c>
-      <c r="E5">
-        <f>_xll.qlDayCounterDayCount(C5,$B$1,$B$2)</f>
-        <v>365</v>
-      </c>
-      <c r="F5">
-        <f>_xll.qlDayCounterYearFraction(C5,$B$1,$B$2,$B$1,$B$2)</f>
-        <v>1.0138888888888888</v>
-      </c>
-      <c r="G5">
-        <f>_xll.qlDayCounterYearFraction(C5,$B$1,$B$2)</f>
-        <v>1.0138888888888888</v>
-      </c>
-      <c r="H5" t="str">
-        <f>_xll.qlDayCounterName(C5)</f>
-        <v>Actual/360</v>
-      </c>
-      <c r="I5" t="b">
-        <f>_xll.qlDayCounterEmpty(C5)</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <f>_xll.qlDayCounterYearFractionToDate(C5,$B$1,F5)</f>
-        <v>29586</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D5" t="e">
+        <f ca="1">_xll.qlDayCounter(C5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E5" t="e">
+        <f ca="1">_xll.qlDayCounterDayCount(C5,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F5" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C5,$B$1,$B$2,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G5" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C5,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H5" t="e">
+        <f ca="1">_xll.qlDayCounterName(C5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I5" t="e">
+        <f ca="1">_xll.qlDayCounterEmpty(C5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J5" s="2" t="e">
+        <f ca="1">_xll.qlDayCounterYearFractionToDate(C5,$B$1,F5)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D6" t="str">
-        <f>_xll.qlDayCounter(C6)</f>
-        <v>Actual/364</v>
-      </c>
-      <c r="E6">
-        <f>_xll.qlDayCounterDayCount(C6,$B$1,$B$2)</f>
-        <v>365</v>
-      </c>
-      <c r="F6">
-        <f>_xll.qlDayCounterYearFraction(C6,$B$1,$B$2,$B$1,$B$2)</f>
-        <v>1.0027472527472527</v>
-      </c>
-      <c r="G6">
-        <f>_xll.qlDayCounterYearFraction(C6,$B$1,$B$2)</f>
-        <v>1.0027472527472527</v>
-      </c>
-      <c r="H6" t="str">
-        <f>_xll.qlDayCounterName(C6)</f>
-        <v>Actual/364</v>
-      </c>
-      <c r="I6" t="b">
-        <f>_xll.qlDayCounterEmpty(C6)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
-        <f>_xll.qlDayCounterYearFractionToDate(C6,$B$1,F6)</f>
-        <v>29586</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D6" t="e">
+        <f ca="1">_xll.qlDayCounter(C6)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E6" t="e">
+        <f ca="1">_xll.qlDayCounterDayCount(C6,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F6" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C6,$B$1,$B$2,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G6" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C6,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H6" t="e">
+        <f ca="1">_xll.qlDayCounterName(C6)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I6" t="e">
+        <f ca="1">_xll.qlDayCounterEmpty(C6)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J6" s="2" t="e">
+        <f ca="1">_xll.qlDayCounterYearFractionToDate(C6,$B$1,F6)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D7" t="str">
-        <f>_xll.qlDayCounter(C7)</f>
-        <v>Actual/365.25</v>
-      </c>
-      <c r="E7">
-        <f>_xll.qlDayCounterDayCount(C7,$B$1,$B$2)</f>
-        <v>365</v>
-      </c>
-      <c r="F7">
-        <f>_xll.qlDayCounterYearFraction(C7,$B$1,$B$2,$B$1,$B$2)</f>
-        <v>0.99931553730321698</v>
-      </c>
-      <c r="G7">
-        <f>_xll.qlDayCounterYearFraction(C7,$B$1,$B$2)</f>
-        <v>0.99931553730321698</v>
-      </c>
-      <c r="H7" t="str">
-        <f>_xll.qlDayCounterName(C7)</f>
-        <v>Actual/365.25</v>
-      </c>
-      <c r="I7" t="b">
-        <f>_xll.qlDayCounterEmpty(C7)</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <f>_xll.qlDayCounterYearFractionToDate(C7,$B$1,F7)</f>
-        <v>29586</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D7" t="e">
+        <f ca="1">_xll.qlDayCounter(C7)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E7" t="e">
+        <f ca="1">_xll.qlDayCounterDayCount(C7,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F7" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C7,$B$1,$B$2,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G7" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C7,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H7" t="e">
+        <f ca="1">_xll.qlDayCounterName(C7)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I7" t="e">
+        <f ca="1">_xll.qlDayCounterEmpty(C7)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J7" s="2" t="e">
+        <f ca="1">_xll.qlDayCounterYearFractionToDate(C7,$B$1,F7)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>3</v>
       </c>
-      <c r="D8" t="str">
-        <f>_xll.qlDayCounter(C8)</f>
-        <v>Actual/365 (Fixed)</v>
-      </c>
-      <c r="E8">
-        <f>_xll.qlDayCounterDayCount(C8,$B$1,$B$2)</f>
-        <v>365</v>
-      </c>
-      <c r="F8">
-        <f>_xll.qlDayCounterYearFraction(C8,$B$1,$B$2,$B$1,$B$2)</f>
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <f>_xll.qlDayCounterYearFraction(C8,$B$1,$B$2)</f>
-        <v>1</v>
-      </c>
-      <c r="H8" t="str">
-        <f>_xll.qlDayCounterName(C8)</f>
-        <v>Actual/365 (Fixed)</v>
-      </c>
-      <c r="I8" t="b">
-        <f>_xll.qlDayCounterEmpty(C8)</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <f>_xll.qlDayCounterYearFractionToDate(C8,$B$1,F8)</f>
-        <v>29586</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D8" t="e">
+        <f ca="1">_xll.qlDayCounter(C8)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E8" t="e">
+        <f ca="1">_xll.qlDayCounterDayCount(C8,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F8" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C8,$B$1,$B$2,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G8" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C8,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H8" t="e">
+        <f ca="1">_xll.qlDayCounterName(C8)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I8" t="e">
+        <f ca="1">_xll.qlDayCounterEmpty(C8)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J8" s="2" t="e">
+        <f ca="1">_xll.qlDayCounterYearFractionToDate(C8,$B$1,F8)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>4</v>
       </c>
-      <c r="D9" t="str">
-        <f>_xll.qlDayCounter(C9)</f>
-        <v>Actual/366</v>
-      </c>
-      <c r="E9">
-        <f>_xll.qlDayCounterDayCount(C9,$B$1,$B$2)</f>
-        <v>365</v>
-      </c>
-      <c r="F9">
-        <f>_xll.qlDayCounterYearFraction(C9,$B$1,$B$2,$B$1,$B$2)</f>
-        <v>0.99726775956284153</v>
-      </c>
-      <c r="G9">
-        <f>_xll.qlDayCounterYearFraction(C9,$B$1,$B$2)</f>
-        <v>0.99726775956284153</v>
-      </c>
-      <c r="H9" t="str">
-        <f>_xll.qlDayCounterName(C9)</f>
-        <v>Actual/366</v>
-      </c>
-      <c r="I9" t="b">
-        <f>_xll.qlDayCounterEmpty(C9)</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="2">
-        <f>_xll.qlDayCounterYearFractionToDate(C9,$B$1,F9)</f>
-        <v>29586</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D9" t="e">
+        <f ca="1">_xll.qlDayCounter(C9)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E9" t="e">
+        <f ca="1">_xll.qlDayCounterDayCount(C9,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F9" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C9,$B$1,$B$2,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G9" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C9,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H9" t="e">
+        <f ca="1">_xll.qlDayCounterName(C9)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I9" t="e">
+        <f ca="1">_xll.qlDayCounterEmpty(C9)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J9" s="2" t="e">
+        <f ca="1">_xll.qlDayCounterYearFractionToDate(C9,$B$1,F9)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>5</v>
       </c>
-      <c r="D10" t="str">
-        <f>_xll.qlDayCounter(C10)</f>
-        <v>Actual/Actual (ISMA)</v>
-      </c>
-      <c r="E10">
-        <f>_xll.qlDayCounterDayCount(C10,$B$1,$B$2)</f>
-        <v>365</v>
-      </c>
-      <c r="F10">
-        <f>_xll.qlDayCounterYearFraction(C10,$B$1,$B$2,$B$1,$B$2)</f>
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <f>_xll.qlDayCounterYearFraction(C10,$B$1,$B$2)</f>
-        <v>1</v>
-      </c>
-      <c r="H10" t="str">
-        <f>_xll.qlDayCounterName(C10)</f>
-        <v>Actual/Actual (ISMA)</v>
-      </c>
-      <c r="I10" t="b">
-        <f>_xll.qlDayCounterEmpty(C10)</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="2">
-        <f>_xll.qlDayCounterYearFractionToDate(C10,$B$1,F10)</f>
-        <v>29586</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D10" t="e">
+        <f ca="1">_xll.qlDayCounter(C10)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E10" t="e">
+        <f ca="1">_xll.qlDayCounterDayCount(C10,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F10" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C10,$B$1,$B$2,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G10" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C10,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H10" t="e">
+        <f ca="1">_xll.qlDayCounterName(C10)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I10" t="e">
+        <f ca="1">_xll.qlDayCounterEmpty(C10)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J10" s="2" t="e">
+        <f ca="1">_xll.qlDayCounterYearFractionToDate(C10,$B$1,F10)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>6</v>
       </c>
-      <c r="D11" t="str">
-        <f>_xll.qlDayCounter(C11)</f>
-        <v>Business/252(Brazil)</v>
-      </c>
-      <c r="E11">
-        <f>_xll.qlDayCounterDayCount(C11,$B$1,$B$2)</f>
-        <v>253</v>
-      </c>
-      <c r="F11">
-        <f>_xll.qlDayCounterYearFraction(C11,$B$1,$B$2,$B$1,$B$2)</f>
-        <v>1.003968253968254</v>
-      </c>
-      <c r="G11">
-        <f>_xll.qlDayCounterYearFraction(C11,$B$1,$B$2)</f>
-        <v>1.003968253968254</v>
-      </c>
-      <c r="H11" t="str">
-        <f>_xll.qlDayCounterName(C11)</f>
-        <v>Business/252(Brazil)</v>
-      </c>
-      <c r="I11" t="b">
-        <f>_xll.qlDayCounterEmpty(C11)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="2">
-        <f>_xll.qlDayCounterYearFractionToDate(C11,$B$1,F11)</f>
-        <v>29586</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D11" t="e">
+        <f ca="1">_xll.qlDayCounter(C11)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E11" t="e">
+        <f ca="1">_xll.qlDayCounterDayCount(C11,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F11" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C11,$B$1,$B$2,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G11" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C11,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H11" t="e">
+        <f ca="1">_xll.qlDayCounterName(C11)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I11" t="e">
+        <f ca="1">_xll.qlDayCounterEmpty(C11)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J11" s="2" t="e">
+        <f ca="1">_xll.qlDayCounterYearFractionToDate(C11,$B$1,F11)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" t="str">
-        <f>_xll.qlDayCounter(C12)</f>
-        <v>1/1</v>
-      </c>
-      <c r="E12">
-        <f>_xll.qlDayCounterDayCount(C12,$B$1,$B$2)</f>
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <f>_xll.qlDayCounterYearFraction(C12,$B$1,$B$2,$B$1,$B$2)</f>
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <f>_xll.qlDayCounterYearFraction(C12,$B$1,$B$2)</f>
-        <v>1</v>
-      </c>
-      <c r="H12" t="str">
-        <f>_xll.qlDayCounterName(C12)</f>
-        <v>1/1</v>
-      </c>
-      <c r="I12" t="b">
-        <f>_xll.qlDayCounterEmpty(C12)</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="2">
-        <f>_xll.qlDayCounterYearFractionToDate(C12,$B$1,F12)</f>
-        <v>29586</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D12" t="e">
+        <f ca="1">_xll.qlDayCounter(C12)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E12" t="e">
+        <f ca="1">_xll.qlDayCounterDayCount(C12,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F12" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C12,$B$1,$B$2,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G12" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C12,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H12" t="e">
+        <f ca="1">_xll.qlDayCounterName(C12)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I12" t="e">
+        <f ca="1">_xll.qlDayCounterEmpty(C12)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J12" s="2" t="e">
+        <f ca="1">_xll.qlDayCounterYearFractionToDate(C12,$B$1,F12)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>8</v>
       </c>
-      <c r="D13" t="str">
-        <f>_xll.qlDayCounter(C13)</f>
-        <v>Simple</v>
-      </c>
-      <c r="E13">
-        <f>_xll.qlDayCounterDayCount(C13,$B$1,$B$2)</f>
-        <v>360</v>
-      </c>
-      <c r="F13">
-        <f>_xll.qlDayCounterYearFraction(C13,$B$1,$B$2,$B$1,$B$2)</f>
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <f>_xll.qlDayCounterYearFraction(C13,$B$1,$B$2)</f>
-        <v>1</v>
-      </c>
-      <c r="H13" t="str">
-        <f>_xll.qlDayCounterName(C13)</f>
-        <v>Simple</v>
-      </c>
-      <c r="I13" t="b">
-        <f>_xll.qlDayCounterEmpty(C13)</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="2">
-        <f>_xll.qlDayCounterYearFractionToDate(C13,$B$1,F13)</f>
-        <v>29586</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D13" t="e">
+        <f ca="1">_xll.qlDayCounter(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E13" t="e">
+        <f ca="1">_xll.qlDayCounterDayCount(C13,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F13" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C13,$B$1,$B$2,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G13" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C13,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H13" t="e">
+        <f ca="1">_xll.qlDayCounterName(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I13" t="e">
+        <f ca="1">_xll.qlDayCounterEmpty(C13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J13" s="2" t="e">
+        <f ca="1">_xll.qlDayCounterYearFractionToDate(C13,$B$1,F13)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>9</v>
       </c>
-      <c r="D14" t="str">
-        <f>_xll.qlDayCounter(C14)</f>
-        <v>30/360 (Bond Basis)</v>
-      </c>
-      <c r="E14">
-        <f>_xll.qlDayCounterDayCount(C14,$B$1,$B$2)</f>
-        <v>360</v>
-      </c>
-      <c r="F14">
-        <f>_xll.qlDayCounterYearFraction(C14,$B$1,$B$2,$B$1,$B$2)</f>
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <f>_xll.qlDayCounterYearFraction(C14,$B$1,$B$2)</f>
-        <v>1</v>
-      </c>
-      <c r="H14" t="str">
-        <f>_xll.qlDayCounterName(C14)</f>
-        <v>30/360 (Bond Basis)</v>
-      </c>
-      <c r="I14" t="b">
-        <f>_xll.qlDayCounterEmpty(C14)</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="2">
-        <f>_xll.qlDayCounterYearFractionToDate(C14,$B$1,F14)</f>
-        <v>29586</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D14" t="e">
+        <f ca="1">_xll.qlDayCounter(C14)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E14" t="e">
+        <f ca="1">_xll.qlDayCounterDayCount(C14,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F14" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C14,$B$1,$B$2,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G14" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C14,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H14" t="e">
+        <f ca="1">_xll.qlDayCounterName(C14)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I14" t="e">
+        <f ca="1">_xll.qlDayCounterEmpty(C14)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J14" s="2" t="e">
+        <f ca="1">_xll.qlDayCounterYearFractionToDate(C14,$B$1,F14)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>10</v>
       </c>
-      <c r="D15" t="str">
-        <f>_xll.qlDayCounter(C15)</f>
-        <v>30/365</v>
-      </c>
-      <c r="E15">
-        <f>_xll.qlDayCounterDayCount(C15,$B$1,$B$2)</f>
-        <v>359</v>
-      </c>
-      <c r="F15">
-        <f>_xll.qlDayCounterYearFraction(C15,$B$1,$B$2,$B$1,$B$2)</f>
-        <v>0.98356164383561639</v>
-      </c>
-      <c r="G15">
-        <f>_xll.qlDayCounterYearFraction(C15,$B$1,$B$2)</f>
-        <v>0.98356164383561639</v>
-      </c>
-      <c r="H15" t="str">
-        <f>_xll.qlDayCounterName(C15)</f>
-        <v>30/365</v>
-      </c>
-      <c r="I15" t="b">
-        <f>_xll.qlDayCounterEmpty(C15)</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="2">
-        <f>_xll.qlDayCounterYearFractionToDate(C15,$B$1,F15)</f>
-        <v>29585</v>
+      <c r="D15" t="e">
+        <f ca="1">_xll.qlDayCounter(C15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E15" t="e">
+        <f ca="1">_xll.qlDayCounterDayCount(C15,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F15" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C15,$B$1,$B$2,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G15" t="e">
+        <f ca="1">_xll.qlDayCounterYearFraction(C15,$B$1,$B$2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H15" t="e">
+        <f ca="1">_xll.qlDayCounterName(C15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I15" t="e">
+        <f ca="1">_xll.qlDayCounterEmpty(C15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J15" s="2" t="e">
+        <f ca="1">_xll.qlDayCounterYearFractionToDate(C15,$B$1,F15)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
